--- a/scripts/test_output.xlsx
+++ b/scripts/test_output.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="JV" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Filter Check" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JV" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filter Check" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,283 +414,362 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Unique S.No.</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>30042026</t>
+          <t>Document Date</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Document Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Company Code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Posting Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Reference.1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Document Header Text</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Exchange rate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Posting Key</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Special G/L ind.</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Cost Center</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Internal Order</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Profit Center</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Business Area</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Assignment Number (20)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Item Text (50)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Ref Key 1</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Ref Key 2</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ref Key 3 (20)</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Trading Partner</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Tax Code</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Withholding tax code</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Withholding tax base amount in document currency</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Contracts</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Revenue Period</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Core Consultant</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Revenue Month</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Reversal Date</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>LEDGER</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>WT CODE1</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>WT Amount</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Inovice Receipt Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>30042026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="D1" t="n">
+      <c r="D2" t="n">
         <v>6000</v>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>30042026</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Invoice No.</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>30042026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>INV1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Revenue Reclass Apr'26</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Based on the formula</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>GL Codes</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Invoice No.</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J2">
+        <f>-SUM(J3:J7)</f>
+        <v/>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>500003</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>682490C510</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>682490C5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>INV1</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>Revenue Reclass Apr'26</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>IC Code</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Capablity Center</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>EmpNo.</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Billable</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>30042026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Document Date</t>
+          <t>30042026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Document Type</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Company Code</t>
-        </is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Posting Date</t>
+          <t>30042026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Reference.1</t>
+          <t>INV1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Document Header Text</t>
+          <t>Revenue Reclass Apr'26</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Exchange rate</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>-100</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Posting Key</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Special G/L ind.</t>
-        </is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>742234</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Cost Center</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Internal Order</t>
+          <t>682490C510</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Profit Center</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Business Area</t>
+          <t>682490C5</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Assignment Number (20)</t>
+          <t>INV1</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Item Text (50)</t>
+          <t>Revenue Reclass Apr'26</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Ref Key 1</t>
+          <t>Billable</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Ref Key 2</t>
+          <t>CC1</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Ref Key 3 (20)</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Trading Partner</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Tax Code</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Withholding tax code</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Withholding tax base amount in document currency</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Contracts</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Revenue Period</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Core Consultant</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Revenue Month</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Reversal Date</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>LEDGER</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>WT CODE1</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>WT Amount</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Inovice Receipt Date</t>
+          <t>30042026</t>
         </is>
       </c>
     </row>
@@ -732,15 +811,15 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>380</v>
+        <v>-10</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>500003</v>
+        <v>842028</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -765,6 +844,16 @@
       <c r="T4" t="inlineStr">
         <is>
           <t>Billable</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>CC1</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>E1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -811,7 +900,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -853,7 +942,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -900,7 +989,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-10</v>
+        <v>-50</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -908,7 +997,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>842028</v>
+        <v>742238</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -942,7 +1031,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -989,7 +1078,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-200</v>
+        <v>-20</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -997,7 +1086,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>742234</v>
+        <v>842028</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1040,187 +1129,9 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>30042026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>30042026</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>INV1</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Revenue Reclass Apr'26</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>-50</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>742238</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>682490C510</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>682490C5</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>INV1</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Revenue Reclass Apr'26</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Billable</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>CC1</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>30042026</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>30042026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>30042026</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>INV1</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Revenue Reclass Apr'26</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>-20</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>842028</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>682490C510</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>682490C5</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>INV1</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Revenue Reclass Apr'26</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Billable</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>CC1</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>30042026</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="J11">
-        <f>ROUND(SUM(J4:J9),2)</f>
+      <c r="J9">
+        <f>ROUND(SUM(J2:J7),2)</f>
         <v/>
       </c>
     </row>

--- a/scripts/test_output.xlsx
+++ b/scripts/test_output.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L2" t="n">
